--- a/outputs/evaluation/architecture/validation/gemini-3-5/CF_M08/run_1/CF_M08_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/validation/gemini-3-5/CF_M08/run_1/CF_M08_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -456,7 +461,10 @@
       <c r="C2" t="n">
         <v>0.9677</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.6897</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -475,6 +483,9 @@
         <v>0.9655</v>
       </c>
       <c r="D3" t="n">
+        <v>0.7179</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.9631</v>
       </c>
     </row>
@@ -491,6 +502,9 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
+        <v>0.4444</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.8155</v>
       </c>
     </row>
@@ -1221,14 +1235,11 @@
           <t>77</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>AU_42</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Client-Server</t>
@@ -1247,14 +1258,11 @@
       <c r="P2" t="n">
         <v>78</v>
       </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M08_P06</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1275,7 +1283,6 @@
       <c r="D3" t="n">
         <v>0.7835</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1296,7 +1303,6 @@
           <t>['AU_06', 'AU_12', 'AU_14', 'AU_16', 'AU_18', 'AU_20', 'AU_22']</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>AU_51</t>
@@ -1307,7 +1313,6 @@
           <t>system service, authentication service, cloud storage service, payment processing service, analytics service, error monitoring service, email service</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1326,7 +1331,6 @@
           <t>CF_M08_AU04, CF_M08_AU10, CF_M08_AU12, CF_M08_AU14, CF_M08_AU16, CF_M08_AU18, CF_M08_AU20</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M08_AU25</t>
@@ -1377,14 +1381,11 @@
           <t>66</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>P_03</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Observer</t>
@@ -1403,14 +1404,11 @@
       <c r="P4" t="n">
         <v>66</v>
       </c>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M08_P04</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1431,7 +1429,6 @@
       <c r="D5" t="n">
         <v>0.8475</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1452,7 +1449,6 @@
           <t>['AU_06', 'AU_09']</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>AU_49</t>
@@ -1463,7 +1459,6 @@
           <t>system service, data service</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1482,7 +1477,6 @@
           <t>CF_M08_AU04, CF_M08_AU08</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M08_AU24</t>
@@ -1533,14 +1527,11 @@
           <t>67</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>P_04</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Singleton</t>
@@ -1559,14 +1550,11 @@
       <c r="P6" t="n">
         <v>67</v>
       </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M08_P05</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1612,13 +1600,11 @@
           <t>['AU_06']</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>AU_12</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Authentication</t>
@@ -1642,13 +1628,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M08_AU10</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1694,13 +1678,11 @@
           <t>['AU_06']</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>AU_22</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Email</t>
@@ -1724,13 +1706,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M08_AU20</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1776,13 +1756,11 @@
           <t>['AU_06']</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>AU_18</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Analytics</t>
@@ -1806,13 +1784,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M08_AU16</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1858,13 +1834,11 @@
           <t>['AU_06']</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>AU_20</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Error monitoring</t>
@@ -1888,13 +1862,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M08_AU18</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1940,13 +1912,11 @@
           <t>['AU_06']</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>AU_16</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Payment processing</t>
@@ -1970,13 +1940,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M08_AU14</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2022,13 +1990,11 @@
           <t>['AU_06']</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>AU_14</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Cloud storage</t>
@@ -2052,13 +2018,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M08_AU12</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2099,14 +2063,11 @@
           <t>66</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>P_02</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Component-based</t>
@@ -2125,14 +2086,11 @@
       <c r="P13" t="n">
         <v>66</v>
       </c>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M08_P03</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2173,14 +2131,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>AU_04</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Security Service</t>
@@ -2204,13 +2159,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CF_M08_AU02</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2251,14 +2204,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>AU_24</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Amazon EC2</t>
@@ -2282,13 +2232,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>CF_M08_AU01</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2334,13 +2282,11 @@
           <t>['AU_06', 'AU_48']</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>AU_08</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>React</t>
@@ -2364,13 +2310,11 @@
           <t>CF_M08_AU04</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>CF_M08_AU06</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2416,13 +2360,11 @@
           <t>['AU_22']</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>AU_23</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Brevo</t>
@@ -2446,13 +2388,11 @@
           <t>CF_M08_AU20</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>CF_M08_AU21</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2493,14 +2433,11 @@
           <t>42</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>AU_09</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Data Service</t>
@@ -2524,13 +2461,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>CF_M08_AU07</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2576,13 +2511,11 @@
           <t>['AU_20']</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>AU_21</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Sentry</t>
@@ -2606,13 +2539,11 @@
           <t>CF_M08_AU18</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>CF_M08_AU19</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2653,14 +2584,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>AU_25</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Docker</t>
@@ -2684,13 +2612,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>CF_M08_AU22</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2736,13 +2662,11 @@
           <t>['AU_09']</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>AU_10</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
@@ -2766,13 +2690,11 @@
           <t>CF_M08_AU07</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>CF_M08_AU08</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2818,13 +2740,11 @@
           <t>['AU_12']</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>AU_13</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>Google</t>
@@ -2848,13 +2768,11 @@
           <t>CF_M08_AU10</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>CF_M08_AU11</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2900,13 +2818,11 @@
           <t>['AU_14']</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>AU_15</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Amazon S3</t>
@@ -2930,13 +2846,11 @@
           <t>CF_M08_AU12</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>CF_M08_AU13</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2982,13 +2896,11 @@
           <t>['AU_16']</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>AU_17</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>Stripe</t>
@@ -3012,13 +2924,11 @@
           <t>CF_M08_AU14</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>CF_M08_AU15</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3064,13 +2974,11 @@
           <t>['AU_46', 'AU_47', 'AU_50']</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>AU_27</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>HTTPS</t>
@@ -3089,14 +2997,11 @@
       <c r="P25" t="n">
         <v>43</v>
       </c>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>CF_M08_AU23</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3137,14 +3042,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>P_01</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Microservices</t>
@@ -3163,14 +3065,11 @@
       <c r="P26" t="n">
         <v>41</v>
       </c>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3216,13 +3115,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>AU_05</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>Traefik</t>
@@ -3246,13 +3143,11 @@
           <t>CF_M08_AU02</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
           <t>CF_M08_AU03</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3293,14 +3188,11 @@
           <t>41, 42</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>AU_06</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>System Service</t>
@@ -3324,13 +3216,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
           <t>CF_M08_AU04</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3376,13 +3266,11 @@
           <t>['AU_06']</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>AU_07</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>Next.js</t>
@@ -3406,13 +3294,11 @@
           <t>CF_M08_AU04</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
           <t>CF_M08_AU05</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3458,13 +3344,11 @@
           <t>['AU_18']</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>AU_19</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>Google Analytics</t>
@@ -3488,13 +3372,11 @@
           <t>CF_M08_AU16</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
           <t>CF_M08_AU17</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3540,13 +3422,11 @@
           <t>['AU_06', 'AU_49', 'AU_52']</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>AU_11</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>Prisma</t>
@@ -3570,13 +3450,11 @@
           <t>CF_M08_P02</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
           <t>CF_M08_AU09</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3650,7 +3528,6 @@
           <t>User</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Usuario: Un usuario es todo individuo o entidad que interactúa con el sistema, puede ser tanto un donante como una empresa.</t>
@@ -3686,7 +3563,6 @@
           <t>Company</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Empresa: Una empresa es un tipo de usuario que puede ofrecer productos con sus respectivas rutas para que los donantes los entreguen, comenzando así a crear una cadena.</t>
@@ -3722,7 +3598,6 @@
           <t>Donor</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Donante: Un donante es un tipo de usuario que contribuye con productos a una empresa.</t>
@@ -3758,7 +3633,6 @@
           <t>HTTP</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Puerto 80 (HTTP): Traefik abre el puerto 80 para manejar tráfico HTTP no seguro</t>
@@ -3794,7 +3668,6 @@
           <t>TypeScript</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Cabe destacar que para desarrollar el sistema se ha empleado el lenguaje TypeScript.</t>
@@ -3830,7 +3703,6 @@
           <t>Auth.js</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Auth.js (@auth/prisma-adapter@1.0.0): Se ha usado para facilitar la integración con Prisma</t>
@@ -3866,7 +3738,6 @@
           <t>AWS SDK</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>AWS (@aws-sdk/client-s3@3.427.0): Se ha usado para interactuar con el servicio S3</t>
@@ -3902,7 +3773,6 @@
           <t>Format.js</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Format.js (@formatjs/intl-localematcher@0.4.0): Es una librería que sirve para la internacionalización (i18n) de aplicaciones.</t>
@@ -3938,7 +3808,6 @@
           <t>Hook Form</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Hook Form (@hookform/resolvers@3.3.4): Este paquete resolvers es una extensión para React Hook Form</t>
@@ -3974,7 +3843,6 @@
           <t>Radix-ui</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Radix-ui: Esta librería incluye una colección de componentes accesibles y estilizados para React</t>
@@ -4010,7 +3878,6 @@
           <t>React email</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>React email: Es un conjunto de herramientas para crear y manejar correos electrónicos en aplicaciones React.</t>
@@ -4046,7 +3913,6 @@
           <t>Slugify</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Slugify (@sindresorhus/slugify@2.2.1): Slugify sirve para convertir cadenas de texto en slugs amigables para la URL.</t>
@@ -4082,7 +3948,6 @@
           <t>Date-fns</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Date-fns (date-fns@3.6.0): Sirve para manejar fechas en JavaScript.</t>
@@ -4118,7 +3983,6 @@
           <t>Eslint</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>Eslint (eslint@8.44.0): Es una librería que se emplea como una herramienta de linting para JavaScript y TypeScript.</t>
@@ -4154,7 +4018,6 @@
           <t>Negotiator</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>Negotiator (negotiator@0.6.3): Es una librería para la negociación de contenido en HTTP.</t>
@@ -4190,7 +4053,6 @@
           <t>Next-intl</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>Next-intl (next-intl@3.4.4): Es una librería de internacionalización para Next.js.</t>
@@ -4226,7 +4088,6 @@
           <t>Nodemailer</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>Nodemailer (nodemailer@6.9.9): Es una herramienta que sirve para enviar correos electrónicos desde aplicaciones Node.js.</t>
@@ -4262,7 +4123,6 @@
           <t>Sharp</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>Sharp (sharp@0.33.2): Es una librería que sirve para el procesamiento de imágenes.</t>
@@ -4298,7 +4158,6 @@
           <t>Vitest</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>Vitest (vitest@1.5.3): Se ha usado como un framework de testing para el proyecto.</t>
@@ -4334,7 +4193,6 @@
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>se ha hecho uso de la herramienta GitLab, la cual facilita el control de versiones</t>
@@ -4370,7 +4228,6 @@
           <t>Terraform</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>Terraform es una herramienta de infraestructura como código que permite definir y gestionar la infraestructura de manera declarativa</t>
@@ -4401,7 +4258,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>security service, system service</t>
@@ -4437,7 +4293,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>security service, system service</t>
@@ -4473,7 +4328,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>system service, react</t>
@@ -4509,7 +4363,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>system service, security service</t>
@@ -4545,7 +4398,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>data service, prisma</t>
@@ -4561,7 +4413,6 @@
           <t>CF_M08_AU24</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>0.7562</v>
       </c>
@@ -4638,7 +4489,6 @@
           <t>ORM</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>(footnote) It is a programming technique to convert data between the type system used in an object-oriented programming language and the use of a relational database as a persistence engine (Atencio 2016).</t>
@@ -4649,7 +4499,6 @@
           <t>AU_49</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>0.7163</v>
       </c>
